--- a/data/availability/projects/palm-hills-developments/palmet.xlsx
+++ b/data/availability/projects/palm-hills-developments/palmet.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for palmet</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -709,7 +719,6 @@
       <c r="G2" t="n">
         <v>168</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -766,7 +775,6 @@
       <c r="G3" t="n">
         <v>126</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -823,7 +831,6 @@
       <c r="G4" t="n">
         <v>155</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -880,7 +887,6 @@
       <c r="G5" t="n">
         <v>185.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -937,7 +943,6 @@
       <c r="G6" t="n">
         <v>178.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -994,7 +999,6 @@
       <c r="G7" t="n">
         <v>180</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1051,7 +1055,6 @@
       <c r="G8" t="n">
         <v>222.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1108,7 +1111,6 @@
       <c r="G9" t="n">
         <v>123.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1165,7 +1167,6 @@
       <c r="G10" t="n">
         <v>190</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1222,7 +1223,6 @@
       <c r="G11" t="n">
         <v>152</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1279,7 +1279,6 @@
       <c r="G12" t="n">
         <v>188.5</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1336,7 +1335,6 @@
       <c r="G13" t="n">
         <v>228</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1393,7 +1391,6 @@
       <c r="G14" t="n">
         <v>254</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1450,7 +1447,6 @@
       <c r="G15" t="n">
         <v>197.5</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1507,7 +1503,6 @@
       <c r="G16" t="n">
         <v>131.5</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1564,7 +1559,6 @@
       <c r="G17" t="n">
         <v>154</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1621,7 +1615,6 @@
       <c r="G18" t="n">
         <v>130.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1678,7 +1671,6 @@
       <c r="G19" t="n">
         <v>192.5</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/palmet.xlsx
+++ b/data/availability/projects/palm-hills-developments/palmet.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
